--- a/lead_generation_forms/007_social_movement_community_registration_form--lead_generation_forms.xlsx
+++ b/lead_generation_forms/007_social_movement_community_registration_form--lead_generation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -719,167 +719,6 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>first_name</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>First Name</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>last_name</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Last Name</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>occupation</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Occupation</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>contact_method</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Contact Method</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>main_motivation</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Main Motivation</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -891,12 +730,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -924,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -941,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -958,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -975,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -992,63 +831,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'mail'}</t>
+          <t>mail</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Mail'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>contact_method_choices</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>{'label':_'phone'}</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>{'label': 'Phone'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>contact_method_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{'label':_'email'}</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>{'label': 'Email'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>contact_method_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>{'label':_'mail'}</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>{'label': 'Mail'}</t>
+          <t>Mail</t>
         </is>
       </c>
     </row>
